--- a/artfynd/A 16943-2026 artfynd.xlsx
+++ b/artfynd/A 16943-2026 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62509207</v>
+        <v>107457766</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Övermora fäbod, Dlr</t>
+          <t>Övermora Fäbodar, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518577.0562399936</v>
+        <v>518517</v>
       </c>
       <c r="R2" t="n">
-        <v>6714570.042694073</v>
+        <v>6714613</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-01-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-11-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Dalafloran [678]   rikligt</t>
+          <t>2013-11-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,40 +756,30 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>skogsmark</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Inge Palmqvist</t>
+          <t>Anders Engström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Inge Palmqvist</t>
+          <t>Via Anders Engström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Dalaflorans databas</t>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>62509203</v>
+        <v>107457767</v>
       </c>
       <c r="B3" t="n">
-        <v>101323</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,37 +787,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222395</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Övermora fäbod, Dlr</t>
+          <t>Övermora Fäbodar, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518517.8245431845</v>
+        <v>518517</v>
       </c>
       <c r="R3" t="n">
-        <v>6714596.288387336</v>
+        <v>6714613</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,27 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2012-01-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-11-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2012-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Dalafloran [678]   enstaka</t>
+          <t>2013-11-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,62 +857,52 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>fäbodvall</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Inge Palmqvist</t>
+          <t>Anders Engström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Inge Palmqvist</t>
+          <t>Via Anders Engström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Dalaflorans databas</t>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>107457766</v>
+        <v>107457768</v>
       </c>
       <c r="B4" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -967,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518516.7537991646</v>
+        <v>518517</v>
       </c>
       <c r="R4" t="n">
-        <v>6714612.999652789</v>
+        <v>6714613</v>
       </c>
       <c r="S4" t="n">
         <v>125</v>
@@ -1000,19 +945,9 @@
           <t>2013-11-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2013-11-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>107457767</v>
+        <v>62509203</v>
       </c>
       <c r="B5" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104253</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1059,37 +989,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>222395</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Övermora Fäbodar, Dlr</t>
+          <t>Övermora fäbod, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518516.7537991646</v>
+        <v>518518</v>
       </c>
       <c r="R5" t="n">
-        <v>6714612.999652789</v>
+        <v>6714596</v>
       </c>
       <c r="S5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1113,22 +1043,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2013-11-07</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-01-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2013-11-07</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-12-31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Dalafloran [678]   enstaka</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,73 +1064,73 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>fäbodvall</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Engström</t>
+          <t>Inge Palmqvist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Anders Engström</t>
+          <t>Inge Palmqvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+          <t>Dalaflorans databas</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>107457768</v>
+        <v>62509207</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Övermora Fäbodar, Dlr</t>
+          <t>Övermora fäbod, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518516.7537991646</v>
+        <v>518577</v>
       </c>
       <c r="R6" t="n">
-        <v>6714612.999652789</v>
+        <v>6714570</v>
       </c>
       <c r="S6" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1229,22 +1154,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2013-11-07</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-01-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2013-11-07</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-12-31</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Dalafloran [678]   rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,21 +1175,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>skogsmark</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Engström</t>
+          <t>Inge Palmqvist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Anders Engström</t>
+          <t>Inge Palmqvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+          <t>Dalaflorans databas</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1203,7 @@
         <v>107457770</v>
       </c>
       <c r="B7" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1315,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518516.7537991646</v>
+        <v>518517</v>
       </c>
       <c r="R7" t="n">
-        <v>6714612.999652789</v>
+        <v>6714613</v>
       </c>
       <c r="S7" t="n">
         <v>125</v>
@@ -1348,19 +1268,9 @@
           <t>2013-11-07</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2013-11-07</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 16943-2026 artfynd.xlsx
+++ b/artfynd/A 16943-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107457766</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107457767</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107457768</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1086,6 +1106,11 @@
           <t>Dalaflorans databas</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62509203</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
           <t>Dalaflorans databas</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62509207</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1298,8 +1328,21 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107457770</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>